--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Pharma Index Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Pharma Index Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="79">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty Pharma Index Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -70,6 +70,12 @@
     <t>Pharmaceuticals &amp; Biotechnology</t>
   </si>
   <si>
+    <t>Divi's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE361B01024</t>
+  </si>
+  <si>
     <t>Cipla Ltd.</t>
   </si>
   <si>
@@ -82,28 +88,28 @@
     <t>INE089A01031</t>
   </si>
   <si>
-    <t>Divi's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE361B01024</t>
-  </si>
-  <si>
     <t>Lupin Ltd.</t>
   </si>
   <si>
     <t>INE326A01037</t>
   </si>
   <si>
+    <t>Torrent Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE685A01028</t>
+  </si>
+  <si>
     <t>Aurobindo Pharma Ltd.</t>
   </si>
   <si>
     <t>INE406A01037</t>
   </si>
   <si>
-    <t>Torrent Pharmaceuticals Ltd.</t>
-  </si>
-  <si>
-    <t>INE685A01028</t>
+    <t>Mankind Pharma Ltd</t>
+  </si>
+  <si>
+    <t>INE634S01028</t>
   </si>
   <si>
     <t>Alkem Laboratories Ltd.</t>
@@ -112,10 +118,10 @@
     <t>INE540L01014</t>
   </si>
   <si>
-    <t>Mankind Pharma Ltd</t>
-  </si>
-  <si>
-    <t>INE634S01028</t>
+    <t>Laurus Labs Ltd.</t>
+  </si>
+  <si>
+    <t>INE947Q01028</t>
   </si>
   <si>
     <t>Zydus Lifesciences Ltd.</t>
@@ -124,12 +130,6 @@
     <t>INE010B01027</t>
   </si>
   <si>
-    <t>Laurus Labs Ltd.</t>
-  </si>
-  <si>
-    <t>INE947Q01028</t>
-  </si>
-  <si>
     <t>Glenmark Pharmaceuticals Ltd.</t>
   </si>
   <si>
@@ -142,16 +142,22 @@
     <t>INE571A01038</t>
   </si>
   <si>
+    <t>Abbott India Ltd.</t>
+  </si>
+  <si>
+    <t>INE358A01014</t>
+  </si>
+  <si>
     <t>Biocon Ltd.</t>
   </si>
   <si>
     <t>INE376G01013</t>
   </si>
   <si>
-    <t>Abbott India Ltd.</t>
-  </si>
-  <si>
-    <t>INE358A01014</t>
+    <t>Gland Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE068V01023</t>
   </si>
   <si>
     <t>J.B.Chemicals &amp; Pharmaceuticals Ltd.</t>
@@ -160,12 +166,6 @@
     <t>INE572A01036</t>
   </si>
   <si>
-    <t>Gland Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE068V01023</t>
-  </si>
-  <si>
     <t>Ajanta Pharma Ltd.</t>
   </si>
   <si>
@@ -241,7 +241,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -251,9 +251,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - Nifty Pharma TRI</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J84"/>
+  <dimension ref="B1:J83"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -1121,10 +1118,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>8637.08</v>
+        <v>8424.000000000002</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9989819302292</v>
+        <v>0.9990358682071998</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1158,10 +1155,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>8637.08</v>
+        <v>8424.000000000002</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9989819302292</v>
+        <v>0.9990358682071998</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1184,13 +1181,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>123741</v>
+        <v>119239</v>
       </c>
       <c r="G8" s="15">
-        <v>2157.98</v>
+        <v>2000.35</v>
       </c>
       <c r="H8" s="16">
-        <v>0.24959627858</v>
+        <v>0.2372295107989</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1213,13 +1210,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>63011</v>
+        <v>14038</v>
       </c>
       <c r="G9" s="15">
-        <v>932.18</v>
+        <v>928.19</v>
       </c>
       <c r="H9" s="16">
-        <v>0.1078178013543</v>
+        <v>0.1100777662051</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1242,13 +1239,13 @@
         <v>17</v>
       </c>
       <c r="F10" s="14">
-        <v>69914</v>
+        <v>62216</v>
       </c>
       <c r="G10" s="15">
-        <v>851.10</v>
+        <v>911.90</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0984399265514</v>
+        <v>0.1081458699215</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1271,13 +1268,13 @@
         <v>17</v>
       </c>
       <c r="F11" s="14">
-        <v>14556</v>
+        <v>67464</v>
       </c>
       <c r="G11" s="15">
-        <v>811.89</v>
+        <v>844.11</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0939048196073</v>
+        <v>0.1001063825633</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1300,13 +1297,13 @@
         <v>17</v>
       </c>
       <c r="F12" s="14">
-        <v>27640</v>
+        <v>26713</v>
       </c>
       <c r="G12" s="15">
-        <v>575.04</v>
+        <v>522.96</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0665102753661</v>
+        <v>0.0620199189978</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1329,13 +1326,13 @@
         <v>17</v>
       </c>
       <c r="F13" s="14">
-        <v>32025</v>
+        <v>11566</v>
       </c>
       <c r="G13" s="15">
-        <v>375.30</v>
+        <v>367.19</v>
       </c>
       <c r="H13" s="16">
-        <v>0.043407947873</v>
+        <v>0.0435465313921</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1358,13 +1355,13 @@
         <v>17</v>
       </c>
       <c r="F14" s="14">
-        <v>10759</v>
+        <v>30928</v>
       </c>
       <c r="G14" s="15">
-        <v>351.72</v>
+        <v>354.99</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0406806379587</v>
+        <v>0.0420996845744</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1387,13 +1384,13 @@
         <v>17</v>
       </c>
       <c r="F15" s="14">
-        <v>6077</v>
+        <v>12483</v>
       </c>
       <c r="G15" s="15">
-        <v>307.68</v>
+        <v>308.04</v>
       </c>
       <c r="H15" s="16">
-        <v>0.035586883564</v>
+        <v>0.0365316962064</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1416,13 +1413,13 @@
         <v>17</v>
       </c>
       <c r="F16" s="14">
-        <v>11898</v>
+        <v>5876</v>
       </c>
       <c r="G16" s="15">
-        <v>289.76</v>
+        <v>299.59</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0335142205587</v>
+        <v>0.0355295768941</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1445,13 +1442,13 @@
         <v>17</v>
       </c>
       <c r="F17" s="14">
-        <v>28659</v>
+        <v>43282</v>
       </c>
       <c r="G17" s="15">
-        <v>278.06</v>
+        <v>263.85</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0321609751814</v>
+        <v>0.0312910272823</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1474,13 +1471,13 @@
         <v>17</v>
       </c>
       <c r="F18" s="14">
-        <v>45088</v>
+        <v>27621</v>
       </c>
       <c r="G18" s="15">
-        <v>263.34</v>
+        <v>256.88</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0304584305699</v>
+        <v>0.0304644270922</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1503,13 +1500,13 @@
         <v>17</v>
       </c>
       <c r="F19" s="14">
-        <v>17249</v>
+        <v>16650</v>
       </c>
       <c r="G19" s="15">
-        <v>250.66</v>
+        <v>242.61</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0289918364344</v>
+        <v>0.0287720906915</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1532,13 +1529,13 @@
         <v>17</v>
       </c>
       <c r="F20" s="14">
-        <v>15548</v>
+        <v>15366</v>
       </c>
       <c r="G20" s="15">
-        <v>224.40</v>
+        <v>218.93</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0259545523653</v>
+        <v>0.0259637847372</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1561,13 +1558,13 @@
         <v>17</v>
       </c>
       <c r="F21" s="14">
-        <v>51557</v>
+        <v>575</v>
       </c>
       <c r="G21" s="15">
-        <v>186.92</v>
+        <v>175.12</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0216195406779</v>
+        <v>0.0207681815337</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1590,13 +1587,13 @@
         <v>17</v>
       </c>
       <c r="F22" s="14">
-        <v>595</v>
+        <v>49805</v>
       </c>
       <c r="G22" s="15">
-        <v>155.73</v>
+        <v>167.27</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0180120429583</v>
+        <v>0.0198372186224</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1619,13 +1616,13 @@
         <v>17</v>
       </c>
       <c r="F23" s="14">
-        <v>8185</v>
+        <v>8798</v>
       </c>
       <c r="G23" s="15">
-        <v>144.38</v>
+        <v>139.77</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0166992792803</v>
+        <v>0.0165758835825</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1648,13 +1645,13 @@
         <v>17</v>
       </c>
       <c r="F24" s="14">
-        <v>9105</v>
+        <v>7933</v>
       </c>
       <c r="G24" s="15">
-        <v>138.83</v>
+        <v>132.98</v>
       </c>
       <c r="H24" s="16">
-        <v>0.016057355191</v>
+        <v>0.0157706303127</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1677,13 +1674,13 @@
         <v>17</v>
       </c>
       <c r="F25" s="14">
-        <v>4811</v>
+        <v>4654</v>
       </c>
       <c r="G25" s="15">
-        <v>129.63</v>
+        <v>116.85</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0149932648089</v>
+        <v>0.0138577090693</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1706,13 +1703,13 @@
         <v>17</v>
       </c>
       <c r="F26" s="14">
-        <v>10241</v>
+        <v>9893</v>
       </c>
       <c r="G26" s="15">
-        <v>120.21</v>
+        <v>87.39</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0139037287871</v>
+        <v>0.0103639297866</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1735,13 +1732,13 @@
         <v>17</v>
       </c>
       <c r="F27" s="14">
-        <v>16585</v>
+        <v>16026</v>
       </c>
       <c r="G27" s="15">
-        <v>92.27</v>
+        <v>85.03</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0106721325612</v>
+        <v>0.0100840479432</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2256,10 +2253,10 @@
         <v>13</v>
       </c>
       <c r="G55" s="9">
-        <v>55.34</v>
+        <v>26.54</v>
       </c>
       <c r="H55" s="10">
-        <v>0.0064007349728</v>
+        <v>0.0031474847984</v>
       </c>
       <c r="I55" s="9" t="s">
         <v>13</v>
@@ -2293,10 +2290,10 @@
         <v>13</v>
       </c>
       <c r="G57" s="18">
-        <v>-46.53788879000058</v>
+        <v>-18.410315700000865</v>
       </c>
       <c r="H57" s="19">
-        <v>-0.005382665203086785</v>
+        <v>-0.002183353006806751</v>
       </c>
       <c r="I57" s="18" t="s">
         <v>13</v>
@@ -2322,10 +2319,10 @@
         <v>13</v>
       </c>
       <c r="G58" s="18">
-        <v>8645.88211121</v>
+        <v>8432.1296843</v>
       </c>
       <c r="H58" s="19">
-        <v>0.9999999999989131</v>
+        <v>0.9999999999987927</v>
       </c>
       <c r="I58" s="18" t="s">
         <v>13</v>
@@ -2398,11 +2395,6 @@
     <row r="83" ht="15">
       <c r="B83" s="21" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="84" ht="15">
-      <c r="B84" s="21" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
